--- a/pc-web/public/import/importCar.xlsx
+++ b/pc-web/public/import/importCar.xlsx
@@ -1,253 +1,184 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="业主车辆信息" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="业主车辆信息" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
-  <si>
-    <t>车辆类型：9901表示家用小汽车，9902表示客车，9903表示货车；
-停车场：停车场编号，系统中不存在自动创建
-车位：停车位编号，系统中不存在自动创建
-起租时间: 格式为YYYY-MM-DD；
-截止时间: 格式为YYYY-MM-DD；
-停车场类型：1001表示地上停车场，2001表示地下停车场；
-车位状态：S表示出售，H表示出租；
-注意：所有单元格式为文本</t>
-  </si>
-  <si>
-    <t>车牌号</t>
-  </si>
-  <si>
-    <t>业主名称</t>
-  </si>
-  <si>
-    <t>手机号</t>
-  </si>
-  <si>
-    <t>车辆品牌</t>
-  </si>
-  <si>
-    <t>车辆类型</t>
-  </si>
-  <si>
-    <t>颜色</t>
-  </si>
-  <si>
-    <t>停车场</t>
-  </si>
-  <si>
-    <t>车位</t>
-  </si>
-  <si>
-    <t>起租时间</t>
-  </si>
-  <si>
-    <t>截止时间</t>
-  </si>
-  <si>
-    <t>停车场类型</t>
-  </si>
-  <si>
-    <t>车位状态</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="21">
     <font>
-      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color indexed="8"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <b val="1"/>
+      <color theme="3"/>
       <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
       <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
+      <b val="1"/>
       <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
+      <b val="1"/>
       <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -547,161 +478,162 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -947,7 +879,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -956,7 +888,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
       <tableStyleElement type="headerRow" dxfId="16"/>
       <tableStyleElement type="totalRow" dxfId="15"/>
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
@@ -969,11 +901,74 @@
       <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1233,55 +1228,91 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:L2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="11" max="11" width="17.125" customWidth="1"/>
+    <col width="17.125" customWidth="1" style="2" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="150" customHeight="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+    <row r="1" ht="150" customHeight="1" s="2">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>车辆类型：9901表示家用小汽车，9902表示客车，9903表示货车；
+停车场：停车场编号，系统中不存在自动创建
+车位：可空，不填表示无固定车位月租车（仅绑定停车场）
+起租时间: 格式为YYYY-MM-DD；
+截止时间: 格式为YYYY-MM-DD；
+停车场类型：1001表示地上停车场，2001表示地下停车场；
+车位状态：S表示出售，H表示出租；
+注意：所有单元格式为文本</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:12">
-      <c r="A2" t="s">
-        <v>1</v>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>车牌号</t>
+        </is>
       </c>
-      <c r="B2" t="s">
-        <v>2</v>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>业主名称</t>
+        </is>
       </c>
-      <c r="C2" t="s">
-        <v>3</v>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>手机号</t>
+        </is>
       </c>
-      <c r="D2" t="s">
-        <v>4</v>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t>车辆品牌</t>
+        </is>
       </c>
-      <c r="E2" t="s">
-        <v>5</v>
+      <c r="E2" s="0" t="inlineStr">
+        <is>
+          <t>车辆类型</t>
+        </is>
       </c>
-      <c r="F2" t="s">
-        <v>6</v>
+      <c r="F2" s="0" t="inlineStr">
+        <is>
+          <t>颜色</t>
+        </is>
       </c>
-      <c r="G2" t="s">
-        <v>7</v>
+      <c r="G2" s="0" t="inlineStr">
+        <is>
+          <t>停车场</t>
+        </is>
       </c>
-      <c r="H2" t="s">
-        <v>8</v>
+      <c r="H2" s="0" t="inlineStr">
+        <is>
+          <t>车位</t>
+        </is>
       </c>
-      <c r="I2" t="s">
-        <v>9</v>
+      <c r="I2" s="0" t="inlineStr">
+        <is>
+          <t>起租时间</t>
+        </is>
       </c>
-      <c r="J2" t="s">
-        <v>10</v>
+      <c r="J2" s="0" t="inlineStr">
+        <is>
+          <t>截止时间</t>
+        </is>
       </c>
-      <c r="K2" t="s">
-        <v>11</v>
+      <c r="K2" s="0" t="inlineStr">
+        <is>
+          <t>停车场类型</t>
+        </is>
       </c>
-      <c r="L2" t="s">
-        <v>12</v>
+      <c r="L2" s="0" t="inlineStr">
+        <is>
+          <t>车位状态</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1289,6 +1320,5 @@
     <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/pc-web/public/import/importCar.xlsx
+++ b/pc-web/public/import/importCar.xlsx
@@ -1233,7 +1233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col width="17.125" customWidth="1" style="2" min="11" max="11"/>
@@ -1242,14 +1242,12 @@
     <row r="1" ht="150" customHeight="1" s="2">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>车辆类型：9901表示家用小汽车，9902表示客车，9903表示货车；
-停车场：停车场编号，系统中不存在自动创建
-车位：可空，不填表示无固定车位月租车（仅绑定停车场）
+          <t>车牌类型：H表示月租车，I表示内部车，NM表示免费车；
+停车场若不存在系统将自动创建；
 起租时间: 格式为YYYY-MM-DD；
 截止时间: 格式为YYYY-MM-DD；
 停车场类型：1001表示地上停车场，2001表示地下停车场；
-车位状态：S表示出售，H表示出租；
-注意：所有单元格式为文本</t>
+注意：所有单元格格式为文本</t>
         </is>
       </c>
     </row>
@@ -1271,47 +1269,32 @@
       </c>
       <c r="D2" s="0" t="inlineStr">
         <is>
-          <t>车辆品牌</t>
+          <t>车辆类型</t>
         </is>
       </c>
       <c r="E2" s="0" t="inlineStr">
         <is>
-          <t>车辆类型</t>
+          <t>停车场</t>
         </is>
       </c>
       <c r="F2" s="0" t="inlineStr">
         <is>
-          <t>颜色</t>
+          <t>起租时间</t>
         </is>
       </c>
       <c r="G2" s="0" t="inlineStr">
         <is>
-          <t>停车场</t>
+          <t>截止时间</t>
         </is>
       </c>
       <c r="H2" s="0" t="inlineStr">
         <is>
-          <t>车位</t>
+          <t>停车场类型</t>
         </is>
       </c>
       <c r="I2" s="0" t="inlineStr">
         <is>
-          <t>起租时间</t>
-        </is>
-      </c>
-      <c r="J2" s="0" t="inlineStr">
-        <is>
-          <t>截止时间</t>
-        </is>
-      </c>
-      <c r="K2" s="0" t="inlineStr">
-        <is>
-          <t>停车场类型</t>
-        </is>
-      </c>
-      <c r="L2" s="0" t="inlineStr">
-        <is>
-          <t>车位状态</t>
+          <t>车牌类型</t>
         </is>
       </c>
     </row>

--- a/pc-web/public/import/importCar.xlsx
+++ b/pc-web/public/import/importCar.xlsx
@@ -1,184 +1,254 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\hcv2\MicroCommunityV2\pc-web\public\import\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="业主车辆信息" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="业主车辆信息" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+  <si>
+    <t>车牌类型：H表示月租车，I表示内部车，NM表示免费车；
+停车场若不存在系统将自动创建；
+起租时间: 格式为YYYY-MM-DD；
+截止时间: 格式为YYYY-MM-DD；
+停车场类型：1001表示地上停车场，2001表示地下停车场；
+停车场：填写系统中存在的停车场编号；
+车辆类型：9901 家用小汽车
+9902 客车
+9903 货车
+9904 电动车
+9905 三轮车
+9906 信用期车辆(1个月)
+注意：所有单元格格式为文本</t>
+  </si>
+  <si>
+    <t>车牌号</t>
+  </si>
+  <si>
+    <t>业主名称</t>
+  </si>
+  <si>
+    <t>手机号</t>
+  </si>
+  <si>
+    <t>车辆类型</t>
+  </si>
+  <si>
+    <t>停车场</t>
+  </si>
+  <si>
+    <t>起租时间</t>
+  </si>
+  <si>
+    <t>截止时间</t>
+  </si>
+  <si>
+    <t>停车场类型</t>
+  </si>
+  <si>
+    <t>车牌类型</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
   <fonts count="21">
     <font>
+      <sz val="11"/>
+      <color indexed="8"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <color indexed="8"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF0000FF"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF800080"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="18"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <i val="1"/>
-      <color rgb="FF7F7F7F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="15"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="13"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF3F3F76"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C0006"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C6500"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="0"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="1"/>
-      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -478,162 +548,162 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -879,7 +949,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -888,7 +958,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
       <tableStyleElement type="headerRow" dxfId="16"/>
       <tableStyleElement type="totalRow" dxfId="15"/>
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
@@ -901,74 +971,11 @@
       <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1228,74 +1235,46 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I2"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col width="17.125" customWidth="1" style="2" min="11" max="11"/>
+    <col min="11" max="11" width="17.125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="150" customHeight="1" s="2">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>车牌类型：H表示月租车，I表示内部车，NM表示免费车；
-停车场若不存在系统将自动创建；
-起租时间: 格式为YYYY-MM-DD；
-截止时间: 格式为YYYY-MM-DD；
-停车场类型：1001表示地上停车场，2001表示地下停车场；
-注意：所有单元格格式为文本</t>
-        </is>
+    <row r="1" ht="150" customHeight="1" spans="1:9">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="0" t="inlineStr">
-        <is>
-          <t>车牌号</t>
-        </is>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>1</v>
       </c>
-      <c r="B2" s="0" t="inlineStr">
-        <is>
-          <t>业主名称</t>
-        </is>
+      <c r="B2" t="s">
+        <v>2</v>
       </c>
-      <c r="C2" s="0" t="inlineStr">
-        <is>
-          <t>手机号</t>
-        </is>
+      <c r="C2" t="s">
+        <v>3</v>
       </c>
-      <c r="D2" s="0" t="inlineStr">
-        <is>
-          <t>车辆类型</t>
-        </is>
+      <c r="D2" t="s">
+        <v>4</v>
       </c>
-      <c r="E2" s="0" t="inlineStr">
-        <is>
-          <t>停车场</t>
-        </is>
+      <c r="E2" t="s">
+        <v>5</v>
       </c>
-      <c r="F2" s="0" t="inlineStr">
-        <is>
-          <t>起租时间</t>
-        </is>
+      <c r="F2" t="s">
+        <v>6</v>
       </c>
-      <c r="G2" s="0" t="inlineStr">
-        <is>
-          <t>截止时间</t>
-        </is>
+      <c r="G2" t="s">
+        <v>7</v>
       </c>
-      <c r="H2" s="0" t="inlineStr">
-        <is>
-          <t>停车场类型</t>
-        </is>
+      <c r="H2" t="s">
+        <v>8</v>
       </c>
-      <c r="I2" s="0" t="inlineStr">
-        <is>
-          <t>车牌类型</t>
-        </is>
+      <c r="I2" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1303,5 +1282,6 @@
     <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>